--- a/data/trans_bre/P1401-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1401-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,83</t>
+          <t>-0,46; 1,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,15</t>
+          <t>0,31; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,8</t>
+          <t>-0,66; 1,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 354,28</t>
+          <t>-36,97; 431,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 793,31</t>
+          <t>3,45; 811,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 156,12</t>
+          <t>-27,1; 137,92</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,12</t>
+          <t>0,06; 2,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,8</t>
+          <t>-0,13; 1,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,06</t>
+          <t>-0,86; 1,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 533,03</t>
+          <t>-6,68; 819,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 441,97</t>
+          <t>-20,24; 497,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 218,21</t>
+          <t>-33,38; 95,14</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-41,89%</t>
+          <t>-23,6%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,31</t>
+          <t>-0,42; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,76</t>
+          <t>-0,2; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,29</t>
+          <t>-1,63; 0,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 543,79</t>
+          <t>-38,48; 434,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 618,55</t>
+          <t>-43,79; 698,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,95; 19,38</t>
+          <t>-59,8; 56,16</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,21</t>
+          <t>-0,59; 2,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,01</t>
+          <t>0,3; 2,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,14</t>
+          <t>-0,95; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 184,92</t>
+          <t>-26,86; 173,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 384,89</t>
+          <t>10,97; 386,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 60,09</t>
+          <t>-30,5; 73,58</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,56</t>
+          <t>0,31; 1,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,81</t>
+          <t>0,51; 1,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,79</t>
+          <t>-0,44; 0,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 170,25</t>
+          <t>19,84; 166,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,74; 254,37</t>
+          <t>47,99; 249,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 48,63</t>
+          <t>-18,13; 41,71</t>
         </is>
       </c>
     </row>
